--- a/xls/dialog_v2.xlsx
+++ b/xls/dialog_v2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
   <si>
     <t>section</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -70,10 +70,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>node_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>label_key</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -98,10 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>condition_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>priority</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -119,10 +111,6 @@
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很高興認識你，我是NPC A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -163,15 +151,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>這是哪裡?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>哪裡可以買吃的?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>沒事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哪裡可以休息?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要買武器？那你得去鎮東邊的『烈焰鍛造坊』！老布隆克的手藝全鎮最好，從短劍到戰斧應有盡有。記住，開門時間是早上日出到傍晚日落。哦，帶足金幣——好貨不便宜！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>餓了嗎？去鎮中央的『胖母雞酒館』！瑪格達大嬸的燉肉鍋湯底用了三天三夜熬製，配上剛出爐的黑麥麵包，保管你吃飽還想再來一碗。若是要帶路的乾糧，後院的市集也有各種蠟封肉乾和果醬。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要歇腳？鎮西的『銀月旅館』是你最好的選擇。掌櫃艾莉亞小姐會為你安排乾淨的房間和熱水澡。一夜住宿含早點只需 5 枚銀幣。若是錢包緊，也可以去酒館角落打地鋪，不過……就別奢望睡得多好了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很高興認識你，我是Karen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -179,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -195,13 +223,46 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -218,11 +279,50 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -519,82 +619,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.875" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="27.75" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="28.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
     <col min="7" max="7" width="10.75" customWidth="1"/>
     <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="9" width="13.75" customWidth="1"/>
-    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
-        <v>25</v>
+      <c r="F1" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7">
         <v>3</v>
       </c>
     </row>
@@ -606,177 +708,504 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
+    <row r="7" spans="1:11" s="2" customFormat="1">
+      <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="I7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J7" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="33">
+      <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="24" spans="2:11" ht="99">
+      <c r="B24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="29" spans="2:11" ht="99">
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="33">
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="34" spans="2:11" ht="99">
+      <c r="B34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E36" s="6"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" t="s">
-        <v>33</v>
-      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/dialog_v2.xlsx
+++ b/xls/dialog_v2.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="karen" sheetId="1" r:id="rId1"/>
-    <sheet name="npc_b" sheetId="2" r:id="rId2"/>
+    <sheet name="xi" sheetId="2" r:id="rId2"/>
     <sheet name="npc_c" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="53">
   <si>
     <t>section</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -151,6 +151,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>這是哪裡?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>哪裡可以買吃的?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,6 +184,9 @@
   </si>
   <si>
     <t>eat</t>
+  </si>
+  <si>
+    <t>eat</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -200,6 +207,26 @@
   </si>
   <si>
     <t>很高興認識你，我是Karen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>餓了嗎？去鎮中央的『胖母雞酒館』！瑪格達大嬸的燉肉鍋湯底用了三天三夜熬製，配上剛出爐的黑麥麵包，保管你吃飽還想再來一碗。若是要帶路的乾糧，後院的市集也有各種蠟封肉乾和果醬。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哦，你連這裡是哪都不知道？看來你是迷路了！這裡是『晨曦小鎮』，坐落於霧谷平原與古松森林之間，是往來東西商旅的必經之地。小鎮雖小，但五臟俱全——鐵匠、酒館、旅館樣樣不缺。據說百年前，一位英雄在此地擊退了黑龍，才讓這片土地得以安居樂業。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很高興認識你，我是Xi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notFlag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -207,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -227,10 +254,16 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="6">
@@ -279,39 +312,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -319,10 +325,46 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -619,593 +661,1061 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:K59"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="28.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="1" max="1" width="3.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9" style="4"/>
+    <col min="3" max="3" width="17.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="18" style="4" customWidth="1"/>
+    <col min="5" max="5" width="28.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.75" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11" s="1" customFormat="1">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="31.5">
+      <c r="B13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" s="16" customFormat="1">
+      <c r="B18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="2:11" s="16" customFormat="1">
+      <c r="B19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="2:11" s="16" customFormat="1">
+      <c r="B20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" spans="2:11" s="16" customFormat="1">
+      <c r="B21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="2:11" s="16" customFormat="1">
+      <c r="B22" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="2:11" s="16" customFormat="1">
+      <c r="B23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="24" spans="2:11" s="16" customFormat="1">
+      <c r="E24" s="17"/>
+    </row>
+    <row r="25" spans="2:11" s="16" customFormat="1" ht="94.5">
+      <c r="B25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+    </row>
+    <row r="26" spans="2:11" s="16" customFormat="1">
+      <c r="B26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" spans="2:11" s="16" customFormat="1">
+      <c r="B27" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" s="14"/>
+    </row>
+    <row r="28" spans="2:11" s="16" customFormat="1">
+      <c r="B28" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="2:11" s="16" customFormat="1">
+      <c r="B29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" s="14"/>
+    </row>
+    <row r="30" spans="2:11" s="16" customFormat="1">
+      <c r="B30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+    </row>
+    <row r="31" spans="2:11" s="16" customFormat="1">
+      <c r="E31" s="17"/>
+    </row>
+    <row r="32" spans="2:11" s="16" customFormat="1" ht="110.25">
+      <c r="B32" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+    </row>
+    <row r="33" spans="2:11" s="16" customFormat="1">
+      <c r="B33" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="14"/>
+    </row>
+    <row r="34" spans="2:11" s="16" customFormat="1">
+      <c r="B34" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="14"/>
+    </row>
+    <row r="35" spans="2:11" s="16" customFormat="1">
+      <c r="B35" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="14"/>
+    </row>
+    <row r="36" spans="2:11" s="16" customFormat="1">
+      <c r="B36" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K36" s="14"/>
+    </row>
+    <row r="37" spans="2:11" s="16" customFormat="1">
+      <c r="B37" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+    </row>
+    <row r="38" spans="2:11" s="16" customFormat="1">
+      <c r="E38" s="17"/>
+    </row>
+    <row r="39" spans="2:11" s="16" customFormat="1" ht="110.25">
+      <c r="B39" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="33">
-      <c r="B13" s="5" t="s">
+      <c r="D39" s="14"/>
+      <c r="E39" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+    </row>
+    <row r="40" spans="2:11" s="16" customFormat="1">
+      <c r="B40" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K40" s="14"/>
+    </row>
+    <row r="41" spans="2:11" s="16" customFormat="1">
+      <c r="B41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K41" s="14"/>
+    </row>
+    <row r="42" spans="2:11" s="16" customFormat="1">
+      <c r="B42" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K42" s="14"/>
+    </row>
+    <row r="43" spans="2:11" s="16" customFormat="1">
+      <c r="B43" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="2:11" s="16" customFormat="1">
+      <c r="B44" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="45" spans="2:11" s="16" customFormat="1">
+      <c r="E45" s="17"/>
+    </row>
+    <row r="46" spans="2:11" s="16" customFormat="1" ht="110.25">
+      <c r="B46" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C46" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+    </row>
+    <row r="47" spans="2:11" s="16" customFormat="1">
+      <c r="B47" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="14"/>
+    </row>
+    <row r="48" spans="2:11" s="16" customFormat="1">
+      <c r="B48" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="49" spans="2:11" s="16" customFormat="1">
+      <c r="B49" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K49" s="14"/>
+    </row>
+    <row r="50" spans="2:11" s="16" customFormat="1">
+      <c r="B50" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" s="14"/>
+    </row>
+    <row r="51" spans="2:11" s="16" customFormat="1">
+      <c r="B51" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="3" t="s">
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+    </row>
+    <row r="52" spans="2:11" s="16" customFormat="1">
+      <c r="E52" s="17"/>
+    </row>
+    <row r="53" spans="2:11" s="16" customFormat="1">
+      <c r="E53" s="17"/>
+    </row>
+    <row r="54" spans="2:11" s="16" customFormat="1" ht="141.75">
+      <c r="B54" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3" t="s">
+      <c r="C54" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="14"/>
+      <c r="E54" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+    </row>
+    <row r="55" spans="2:11" s="16" customFormat="1">
+      <c r="B55" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="14"/>
+    </row>
+    <row r="56" spans="2:11" s="16" customFormat="1">
+      <c r="B56" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
+      <c r="E56" s="15"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J56" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K56" s="14"/>
+    </row>
+    <row r="57" spans="2:11" s="16" customFormat="1">
+      <c r="B57" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K57" s="14"/>
+    </row>
+    <row r="58" spans="2:11" s="16" customFormat="1">
+      <c r="B58" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
+      <c r="E58" s="15"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" s="14"/>
+    </row>
+    <row r="59" spans="2:11" s="16" customFormat="1">
+      <c r="B59" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="2:11">
-      <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
+      <c r="E59" s="15"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="24" spans="2:11" ht="99">
-      <c r="B24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-    </row>
-    <row r="29" spans="2:11" ht="99">
-      <c r="B29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="34" spans="2:11" ht="99">
-      <c r="B34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1216,9 +1726,1063 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData/>
+  <dimension ref="A1:K59"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="3.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9" style="4"/>
+    <col min="3" max="3" width="17.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="18" style="4" customWidth="1"/>
+    <col min="5" max="5" width="28.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.75" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="1" customFormat="1">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="31.5">
+      <c r="B13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" s="16" customFormat="1">
+      <c r="B18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="2:11" s="16" customFormat="1">
+      <c r="B19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="2:11" s="16" customFormat="1">
+      <c r="B20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" spans="2:11" s="16" customFormat="1">
+      <c r="B21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="2:11" s="16" customFormat="1">
+      <c r="B22" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="2:11" s="16" customFormat="1">
+      <c r="B23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="24" spans="2:11" s="16" customFormat="1">
+      <c r="E24" s="17"/>
+    </row>
+    <row r="25" spans="2:11" s="16" customFormat="1" ht="94.5">
+      <c r="B25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+    </row>
+    <row r="26" spans="2:11" s="16" customFormat="1">
+      <c r="B26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" spans="2:11" s="16" customFormat="1">
+      <c r="B27" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" s="14"/>
+    </row>
+    <row r="28" spans="2:11" s="16" customFormat="1">
+      <c r="B28" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="2:11" s="16" customFormat="1">
+      <c r="B29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" s="14"/>
+    </row>
+    <row r="30" spans="2:11" s="16" customFormat="1">
+      <c r="B30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+    </row>
+    <row r="31" spans="2:11" s="16" customFormat="1">
+      <c r="E31" s="17"/>
+    </row>
+    <row r="32" spans="2:11" s="16" customFormat="1" ht="110.25">
+      <c r="B32" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+    </row>
+    <row r="33" spans="2:11" s="16" customFormat="1">
+      <c r="B33" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="14"/>
+    </row>
+    <row r="34" spans="2:11" s="16" customFormat="1">
+      <c r="B34" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="14"/>
+    </row>
+    <row r="35" spans="2:11" s="16" customFormat="1">
+      <c r="B35" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="14"/>
+    </row>
+    <row r="36" spans="2:11" s="16" customFormat="1">
+      <c r="B36" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K36" s="14"/>
+    </row>
+    <row r="37" spans="2:11" s="16" customFormat="1">
+      <c r="B37" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+    </row>
+    <row r="38" spans="2:11" s="16" customFormat="1">
+      <c r="E38" s="17"/>
+    </row>
+    <row r="39" spans="2:11" s="16" customFormat="1" ht="110.25">
+      <c r="B39" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+    </row>
+    <row r="40" spans="2:11" s="16" customFormat="1">
+      <c r="B40" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K40" s="14"/>
+    </row>
+    <row r="41" spans="2:11" s="16" customFormat="1">
+      <c r="B41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K41" s="14"/>
+    </row>
+    <row r="42" spans="2:11" s="16" customFormat="1">
+      <c r="B42" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K42" s="14"/>
+    </row>
+    <row r="43" spans="2:11" s="16" customFormat="1">
+      <c r="B43" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="2:11" s="16" customFormat="1">
+      <c r="B44" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="45" spans="2:11" s="16" customFormat="1">
+      <c r="E45" s="17"/>
+    </row>
+    <row r="46" spans="2:11" s="16" customFormat="1" ht="110.25">
+      <c r="B46" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+    </row>
+    <row r="47" spans="2:11" s="16" customFormat="1">
+      <c r="B47" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="14"/>
+    </row>
+    <row r="48" spans="2:11" s="16" customFormat="1">
+      <c r="B48" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="49" spans="2:11" s="16" customFormat="1">
+      <c r="B49" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K49" s="14"/>
+    </row>
+    <row r="50" spans="2:11" s="16" customFormat="1">
+      <c r="B50" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" s="14"/>
+    </row>
+    <row r="51" spans="2:11" s="16" customFormat="1">
+      <c r="B51" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+    </row>
+    <row r="52" spans="2:11" s="16" customFormat="1">
+      <c r="E52" s="17"/>
+    </row>
+    <row r="53" spans="2:11" s="16" customFormat="1">
+      <c r="E53" s="17"/>
+    </row>
+    <row r="54" spans="2:11" s="16" customFormat="1" ht="141.75">
+      <c r="B54" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="14"/>
+      <c r="E54" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+    </row>
+    <row r="55" spans="2:11" s="16" customFormat="1">
+      <c r="B55" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="14"/>
+    </row>
+    <row r="56" spans="2:11" s="16" customFormat="1">
+      <c r="B56" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J56" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K56" s="14"/>
+    </row>
+    <row r="57" spans="2:11" s="16" customFormat="1">
+      <c r="B57" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K57" s="14"/>
+    </row>
+    <row r="58" spans="2:11" s="16" customFormat="1">
+      <c r="B58" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" s="14"/>
+    </row>
+    <row r="59" spans="2:11" s="16" customFormat="1">
+      <c r="B59" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="15"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>

--- a/xls/dialog_v2.xlsx
+++ b/xls/dialog_v2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="84">
   <si>
     <t>section</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -138,10 +138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>setFlag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>choice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -162,17 +158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>quest q_karen_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_where=false;
-_weapon=false;
-_eat=false;
-_rest=false</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>_where!=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -186,22 +171,6 @@
   </si>
   <si>
     <t>_rest!=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_weapon=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_eat=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_rest=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_where=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -212,10 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_first_meet=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>post</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -264,18 +229,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>effect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>n_quest_01_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_quest=n_quest_01_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>任務如何了?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,26 +241,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>!_first_meet : _quest=n_quest_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>關於黑森林討伐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>qk01_talk_xi=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rm qk01_start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qk01_start==true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>n_qk01_start</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -328,11 +269,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_quest=n_quest_01_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>處理中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n_quest_01_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01_start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!_first_meet : set _quest n_quest_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set _first_meet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set _weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set _eat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set _rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clr _where;
+clr _weapon;
+clr _eat;
+clr _rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set _where</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01==going</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01==done</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01==close</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set qk01_report</t>
+  </si>
+  <si>
+    <t>rm qk01_start ;
+set qk01_talk_xi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quest q_karen_01 ;
+set _quest n_quest_01_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clr _where ;
+clr _weapon ;
+clr _eat ;
+clr _rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quest q_karen_01 ;
+set _quest n_quest_01_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01==going : 任務如何了?;
+qk01==done : 很好，這是你的獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!_first_meet :
+很高興認識你，我是Karen;
+true :
+你好;需要幫助嗎?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -938,22 +971,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="3.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="20.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="32.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="40.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="34.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -970,22 +1002,19 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="I1" s="37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
@@ -996,49 +1025,46 @@
       <c r="E2" s="8"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="9">
+      <c r="H2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="63">
+    <row r="3" spans="1:9" ht="63">
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="9">
+      <c r="I3" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:9">
       <c r="B4" s="10" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="13"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="I4" s="13"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1046,7 +1072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1">
+    <row r="7" spans="1:9" s="1" customFormat="1">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -1063,39 +1089,35 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="I7" s="37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="63">
+    <row r="8" spans="1:9" ht="63">
       <c r="B8" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9" s="14" t="s">
         <v>11</v>
       </c>
@@ -1104,17 +1126,16 @@
         <v>15</v>
       </c>
       <c r="E9" s="16"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="17">
+      <c r="I9" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:9">
       <c r="B10" s="14" t="s">
         <v>11</v>
       </c>
@@ -1124,35 +1145,33 @@
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="17">
+      <c r="G10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="17">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:9">
       <c r="B11" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="17">
+      <c r="G11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="17">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:9">
       <c r="B12" s="14" t="s">
         <v>11</v>
       </c>
@@ -1161,37 +1180,35 @@
         <v>17</v>
       </c>
       <c r="E12" s="16"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="15" t="s">
         <v>14</v>
       </c>
+      <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="17">
+      <c r="I12" s="17">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:9">
       <c r="B13" s="18" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
       <c r="E13" s="20"/>
       <c r="F13" s="19" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="21"/>
-    </row>
-    <row r="15" spans="1:10" s="4" customFormat="1">
+      <c r="I13" s="21"/>
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1">
       <c r="B15" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="24" t="s">
@@ -1200,10 +1217,9 @@
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="25"/>
-    </row>
-    <row r="16" spans="1:10" s="4" customFormat="1">
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:9" s="4" customFormat="1">
       <c r="B16" s="26" t="s">
         <v>11</v>
       </c>
@@ -1213,16 +1229,15 @@
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H16" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="29"/>
-    </row>
-    <row r="17" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I16" s="29"/>
+    </row>
+    <row r="17" spans="2:9" s="4" customFormat="1">
       <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
@@ -1232,16 +1247,15 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
+      <c r="G17" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H17" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="29"/>
-    </row>
-    <row r="18" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I17" s="29"/>
+    </row>
+    <row r="18" spans="2:9" s="4" customFormat="1">
       <c r="B18" s="26" t="s">
         <v>11</v>
       </c>
@@ -1251,16 +1265,15 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
+      <c r="G18" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H18" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="29"/>
-    </row>
-    <row r="19" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I18" s="29"/>
+    </row>
+    <row r="19" spans="2:9" s="4" customFormat="1">
       <c r="B19" s="26" t="s">
         <v>11</v>
       </c>
@@ -1270,16 +1283,15 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
+      <c r="G19" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H19" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" s="29"/>
-    </row>
-    <row r="20" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I19" s="29"/>
+    </row>
+    <row r="20" spans="2:9" s="4" customFormat="1">
       <c r="B20" s="30" t="s">
         <v>11</v>
       </c>
@@ -1289,36 +1301,34 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="31"/>
-      <c r="J20" s="33"/>
-    </row>
-    <row r="21" spans="2:10" s="4" customFormat="1">
+      <c r="G20" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="31"/>
+      <c r="I20" s="33"/>
+    </row>
+    <row r="21" spans="2:9" s="4" customFormat="1">
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="2:10" s="4" customFormat="1" ht="94.5">
+    <row r="22" spans="2:9" s="4" customFormat="1" ht="78.75">
       <c r="B22" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="24" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="25"/>
-    </row>
-    <row r="23" spans="2:10" s="4" customFormat="1">
+      <c r="I22" s="25"/>
+    </row>
+    <row r="23" spans="2:9" s="4" customFormat="1">
       <c r="B23" s="26" t="s">
         <v>11</v>
       </c>
@@ -1328,16 +1338,15 @@
       </c>
       <c r="E23" s="28"/>
       <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="G23" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H23" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" s="29"/>
-    </row>
-    <row r="24" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I23" s="29"/>
+    </row>
+    <row r="24" spans="2:9" s="4" customFormat="1">
       <c r="B24" s="26" t="s">
         <v>11</v>
       </c>
@@ -1347,16 +1356,15 @@
       </c>
       <c r="E24" s="28"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="G24" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H24" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="29"/>
-    </row>
-    <row r="25" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I24" s="29"/>
+    </row>
+    <row r="25" spans="2:9" s="4" customFormat="1">
       <c r="B25" s="26" t="s">
         <v>11</v>
       </c>
@@ -1366,16 +1374,15 @@
       </c>
       <c r="E25" s="28"/>
       <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
+      <c r="G25" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H25" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="29"/>
-    </row>
-    <row r="26" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I25" s="29"/>
+    </row>
+    <row r="26" spans="2:9" s="4" customFormat="1">
       <c r="B26" s="26" t="s">
         <v>11</v>
       </c>
@@ -1385,16 +1392,15 @@
       </c>
       <c r="E26" s="28"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
+      <c r="G26" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H26" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J26" s="29"/>
-    </row>
-    <row r="27" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I26" s="29"/>
+    </row>
+    <row r="27" spans="2:9" s="4" customFormat="1">
       <c r="B27" s="30" t="s">
         <v>11</v>
       </c>
@@ -1404,36 +1410,34 @@
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" s="31"/>
-      <c r="J27" s="33"/>
-    </row>
-    <row r="28" spans="2:10" s="4" customFormat="1">
+      <c r="G27" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="31"/>
+      <c r="I27" s="33"/>
+    </row>
+    <row r="28" spans="2:9" s="4" customFormat="1">
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="2:10" s="4" customFormat="1" ht="110.25">
+    <row r="29" spans="2:9" s="4" customFormat="1" ht="78.75">
       <c r="B29" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="24" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="25"/>
-    </row>
-    <row r="30" spans="2:10" s="4" customFormat="1">
+      <c r="I29" s="25"/>
+    </row>
+    <row r="30" spans="2:9" s="4" customFormat="1">
       <c r="B30" s="26" t="s">
         <v>11</v>
       </c>
@@ -1443,16 +1447,15 @@
       </c>
       <c r="E30" s="28"/>
       <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
+      <c r="G30" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H30" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I30" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J30" s="29"/>
-    </row>
-    <row r="31" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I30" s="29"/>
+    </row>
+    <row r="31" spans="2:9" s="4" customFormat="1">
       <c r="B31" s="26" t="s">
         <v>11</v>
       </c>
@@ -1462,16 +1465,15 @@
       </c>
       <c r="E31" s="28"/>
       <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
+      <c r="G31" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H31" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J31" s="29"/>
-    </row>
-    <row r="32" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I31" s="29"/>
+    </row>
+    <row r="32" spans="2:9" s="4" customFormat="1">
       <c r="B32" s="26" t="s">
         <v>11</v>
       </c>
@@ -1481,16 +1483,15 @@
       </c>
       <c r="E32" s="28"/>
       <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="G32" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H32" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I32" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="29"/>
-    </row>
-    <row r="33" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I32" s="29"/>
+    </row>
+    <row r="33" spans="2:9" s="4" customFormat="1">
       <c r="B33" s="26" t="s">
         <v>11</v>
       </c>
@@ -1500,16 +1501,15 @@
       </c>
       <c r="E33" s="28"/>
       <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="G33" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H33" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I33" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J33" s="29"/>
-    </row>
-    <row r="34" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I33" s="29"/>
+    </row>
+    <row r="34" spans="2:9" s="4" customFormat="1">
       <c r="B34" s="30" t="s">
         <v>11</v>
       </c>
@@ -1519,36 +1519,34 @@
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I34" s="31"/>
-      <c r="J34" s="33"/>
-    </row>
-    <row r="35" spans="2:10" s="4" customFormat="1">
+      <c r="G34" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="31"/>
+      <c r="I34" s="33"/>
+    </row>
+    <row r="35" spans="2:9" s="4" customFormat="1">
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="2:10" s="4" customFormat="1" ht="110.25">
+    <row r="36" spans="2:9" s="4" customFormat="1" ht="78.75">
       <c r="B36" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="24" t="s">
         <v>26</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="25"/>
-    </row>
-    <row r="37" spans="2:10" s="4" customFormat="1">
+      <c r="I36" s="25"/>
+    </row>
+    <row r="37" spans="2:9" s="4" customFormat="1">
       <c r="B37" s="26" t="s">
         <v>11</v>
       </c>
@@ -1558,16 +1556,15 @@
       </c>
       <c r="E37" s="28"/>
       <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="G37" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H37" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I37" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J37" s="29"/>
-    </row>
-    <row r="38" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I37" s="29"/>
+    </row>
+    <row r="38" spans="2:9" s="4" customFormat="1">
       <c r="B38" s="26" t="s">
         <v>11</v>
       </c>
@@ -1577,16 +1574,15 @@
       </c>
       <c r="E38" s="28"/>
       <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="G38" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H38" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I38" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="29"/>
-    </row>
-    <row r="39" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I38" s="29"/>
+    </row>
+    <row r="39" spans="2:9" s="4" customFormat="1">
       <c r="B39" s="26" t="s">
         <v>11</v>
       </c>
@@ -1596,16 +1592,15 @@
       </c>
       <c r="E39" s="28"/>
       <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="G39" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H39" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="29"/>
-    </row>
-    <row r="40" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I39" s="29"/>
+    </row>
+    <row r="40" spans="2:9" s="4" customFormat="1">
       <c r="B40" s="26" t="s">
         <v>11</v>
       </c>
@@ -1615,16 +1610,15 @@
       </c>
       <c r="E40" s="28"/>
       <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="G40" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H40" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I40" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="29"/>
-    </row>
-    <row r="41" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I40" s="29"/>
+    </row>
+    <row r="41" spans="2:9" s="4" customFormat="1">
       <c r="B41" s="30" t="s">
         <v>11</v>
       </c>
@@ -1634,39 +1628,37 @@
       </c>
       <c r="E41" s="32"/>
       <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="31"/>
-      <c r="J41" s="33"/>
-    </row>
-    <row r="42" spans="2:10" s="4" customFormat="1">
+      <c r="G41" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H41" s="31"/>
+      <c r="I41" s="33"/>
+    </row>
+    <row r="42" spans="2:9" s="4" customFormat="1">
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="2:10" s="4" customFormat="1">
+    <row r="43" spans="2:9" s="4" customFormat="1">
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="2:10" s="4" customFormat="1" ht="141.75">
+    <row r="44" spans="2:9" s="4" customFormat="1" ht="110.25">
       <c r="B44" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="25"/>
-    </row>
-    <row r="45" spans="2:10" s="4" customFormat="1">
+      <c r="I44" s="25"/>
+    </row>
+    <row r="45" spans="2:9" s="4" customFormat="1">
       <c r="B45" s="26" t="s">
         <v>11</v>
       </c>
@@ -1676,16 +1668,15 @@
       </c>
       <c r="E45" s="28"/>
       <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
+      <c r="G45" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H45" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I45" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J45" s="29"/>
-    </row>
-    <row r="46" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I45" s="29"/>
+    </row>
+    <row r="46" spans="2:9" s="4" customFormat="1">
       <c r="B46" s="26" t="s">
         <v>11</v>
       </c>
@@ -1695,16 +1686,15 @@
       </c>
       <c r="E46" s="28"/>
       <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="G46" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H46" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I46" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J46" s="29"/>
-    </row>
-    <row r="47" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I46" s="29"/>
+    </row>
+    <row r="47" spans="2:9" s="4" customFormat="1">
       <c r="B47" s="26" t="s">
         <v>11</v>
       </c>
@@ -1714,16 +1704,15 @@
       </c>
       <c r="E47" s="28"/>
       <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
+      <c r="G47" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H47" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I47" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J47" s="29"/>
-    </row>
-    <row r="48" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I47" s="29"/>
+    </row>
+    <row r="48" spans="2:9" s="4" customFormat="1">
       <c r="B48" s="26" t="s">
         <v>11</v>
       </c>
@@ -1733,16 +1722,15 @@
       </c>
       <c r="E48" s="28"/>
       <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="G48" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H48" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I48" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J48" s="29"/>
-    </row>
-    <row r="49" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I48" s="29"/>
+    </row>
+    <row r="49" spans="2:9" s="4" customFormat="1">
       <c r="B49" s="30" t="s">
         <v>11</v>
       </c>
@@ -1752,135 +1740,165 @@
       </c>
       <c r="E49" s="32"/>
       <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="31"/>
-      <c r="J49" s="33"/>
-    </row>
-    <row r="51" spans="2:10">
+      <c r="G49" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" s="31"/>
+      <c r="I49" s="33"/>
+    </row>
+    <row r="51" spans="2:9">
       <c r="B51" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F51" s="23"/>
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="25"/>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="I51" s="25"/>
+    </row>
+    <row r="52" spans="2:9" ht="31.5">
       <c r="B52" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="27"/>
       <c r="D52" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52" s="28"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H52" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="I52" s="27"/>
-      <c r="J52" s="29"/>
-    </row>
-    <row r="53" spans="2:10">
+      <c r="F52" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H52" s="27"/>
+      <c r="I52" s="29"/>
+    </row>
+    <row r="53" spans="2:9">
       <c r="B53" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="31"/>
       <c r="D53" s="31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E53" s="32"/>
       <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="31"/>
-      <c r="J53" s="33"/>
-    </row>
-    <row r="55" spans="2:10">
+      <c r="G53" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H53" s="31"/>
+      <c r="I53" s="33"/>
+    </row>
+    <row r="55" spans="2:9">
       <c r="B55" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D55" s="23"/>
       <c r="E55" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55" s="23" t="s">
-        <v>76</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F55" s="23"/>
       <c r="G55" s="23"/>
       <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="25"/>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="I55" s="25"/>
+    </row>
+    <row r="56" spans="2:9">
       <c r="B56" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="31"/>
       <c r="D56" s="31" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I56" s="31"/>
-      <c r="J56" s="33"/>
-    </row>
-    <row r="58" spans="2:10">
+      <c r="G56" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H56" s="31"/>
+      <c r="I56" s="33"/>
+    </row>
+    <row r="58" spans="2:9" ht="31.5">
       <c r="B58" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="24" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="25"/>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31" t="s">
+      <c r="I58" s="25"/>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" s="28"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="H59" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="I59" s="29"/>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" s="32"/>
+      <c r="F60" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="E59" s="32"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I59" s="31"/>
-      <c r="J59" s="33"/>
+      <c r="G60" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H60" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="I60" s="33"/>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="32"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H61" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="I61" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1891,7 +1909,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="3.875" style="2" customWidth="1"/>
@@ -1899,14 +1917,13 @@
     <col min="3" max="3" width="20.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="32.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="32.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1923,22 +1940,19 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="I1" s="37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1949,49 +1963,46 @@
       <c r="E2" s="8"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="9">
+      <c r="I2" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="63">
+    <row r="3" spans="1:9" ht="63">
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="9">
+      <c r="I3" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:9">
       <c r="B4" s="10" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="13"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="I4" s="13"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1999,7 +2010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1">
+    <row r="7" spans="1:9" s="1" customFormat="1">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -2016,39 +2027,35 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="I7" s="37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="63">
+    <row r="8" spans="1:9" ht="63">
       <c r="B8" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9" s="14" t="s">
         <v>11</v>
       </c>
@@ -2057,17 +2064,16 @@
         <v>15</v>
       </c>
       <c r="E9" s="16"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="17">
+      <c r="I9" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:9">
       <c r="B10" s="14" t="s">
         <v>11</v>
       </c>
@@ -2077,56 +2083,53 @@
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="17">
+      <c r="G10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="17">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:9">
       <c r="B11" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="17">
+      <c r="G11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="17">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:9">
       <c r="B12" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="G12" s="15" t="s">
+        <v>56</v>
+      </c>
       <c r="H12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" s="17">
+        <v>65</v>
+      </c>
+      <c r="I12" s="17">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:9">
       <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
@@ -2135,37 +2138,35 @@
         <v>17</v>
       </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15" t="s">
+      <c r="F13" s="15" t="s">
         <v>14</v>
       </c>
+      <c r="G13" s="15"/>
       <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="17">
+      <c r="I13" s="17">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:9">
       <c r="B14" s="18" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="21"/>
-    </row>
-    <row r="16" spans="1:10" s="4" customFormat="1">
+      <c r="I14" s="21"/>
+    </row>
+    <row r="16" spans="1:9" s="4" customFormat="1">
       <c r="B16" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="24" t="s">
@@ -2174,10 +2175,9 @@
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="25"/>
-    </row>
-    <row r="17" spans="2:10" s="4" customFormat="1">
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="2:9" s="4" customFormat="1">
       <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
@@ -2187,16 +2187,15 @@
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
+      <c r="G17" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H17" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J17" s="29"/>
-    </row>
-    <row r="18" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I17" s="29"/>
+    </row>
+    <row r="18" spans="2:9" s="4" customFormat="1">
       <c r="B18" s="26" t="s">
         <v>11</v>
       </c>
@@ -2206,16 +2205,15 @@
       </c>
       <c r="E18" s="28"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
+      <c r="G18" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H18" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="29"/>
-    </row>
-    <row r="19" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I18" s="29"/>
+    </row>
+    <row r="19" spans="2:9" s="4" customFormat="1">
       <c r="B19" s="26" t="s">
         <v>11</v>
       </c>
@@ -2225,16 +2223,15 @@
       </c>
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
+      <c r="G19" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H19" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J19" s="29"/>
-    </row>
-    <row r="20" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I19" s="29"/>
+    </row>
+    <row r="20" spans="2:9" s="4" customFormat="1">
       <c r="B20" s="26" t="s">
         <v>11</v>
       </c>
@@ -2244,16 +2241,15 @@
       </c>
       <c r="E20" s="28"/>
       <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
+      <c r="G20" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H20" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" s="29"/>
-    </row>
-    <row r="21" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I20" s="29"/>
+    </row>
+    <row r="21" spans="2:9" s="4" customFormat="1">
       <c r="B21" s="30" t="s">
         <v>11</v>
       </c>
@@ -2263,36 +2259,34 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" s="31"/>
-      <c r="J21" s="33"/>
-    </row>
-    <row r="22" spans="2:10" s="4" customFormat="1">
+      <c r="G21" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" s="31"/>
+      <c r="I21" s="33"/>
+    </row>
+    <row r="22" spans="2:9" s="4" customFormat="1">
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="2:10" s="4" customFormat="1" ht="94.5">
+    <row r="23" spans="2:9" s="4" customFormat="1" ht="94.5">
       <c r="B23" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="24" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="25"/>
-    </row>
-    <row r="24" spans="2:10" s="4" customFormat="1">
+      <c r="I23" s="25"/>
+    </row>
+    <row r="24" spans="2:9" s="4" customFormat="1">
       <c r="B24" s="26" t="s">
         <v>11</v>
       </c>
@@ -2302,16 +2296,15 @@
       </c>
       <c r="E24" s="28"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="G24" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H24" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J24" s="29"/>
-    </row>
-    <row r="25" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I24" s="29"/>
+    </row>
+    <row r="25" spans="2:9" s="4" customFormat="1">
       <c r="B25" s="26" t="s">
         <v>11</v>
       </c>
@@ -2321,16 +2314,15 @@
       </c>
       <c r="E25" s="28"/>
       <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
+      <c r="G25" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H25" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="29"/>
-    </row>
-    <row r="26" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I25" s="29"/>
+    </row>
+    <row r="26" spans="2:9" s="4" customFormat="1">
       <c r="B26" s="26" t="s">
         <v>11</v>
       </c>
@@ -2340,16 +2332,15 @@
       </c>
       <c r="E26" s="28"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
+      <c r="G26" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H26" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="29"/>
-    </row>
-    <row r="27" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I26" s="29"/>
+    </row>
+    <row r="27" spans="2:9" s="4" customFormat="1">
       <c r="B27" s="26" t="s">
         <v>11</v>
       </c>
@@ -2359,16 +2350,15 @@
       </c>
       <c r="E27" s="28"/>
       <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
+      <c r="G27" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H27" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J27" s="29"/>
-    </row>
-    <row r="28" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I27" s="29"/>
+    </row>
+    <row r="28" spans="2:9" s="4" customFormat="1">
       <c r="B28" s="30" t="s">
         <v>11</v>
       </c>
@@ -2378,36 +2368,34 @@
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="31"/>
-      <c r="J28" s="33"/>
-    </row>
-    <row r="29" spans="2:10" s="4" customFormat="1">
+      <c r="G28" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="31"/>
+      <c r="I28" s="33"/>
+    </row>
+    <row r="29" spans="2:9" s="4" customFormat="1">
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="2:10" s="4" customFormat="1" ht="110.25">
+    <row r="30" spans="2:9" s="4" customFormat="1" ht="110.25">
       <c r="B30" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="24" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="25"/>
-    </row>
-    <row r="31" spans="2:10" s="4" customFormat="1">
+      <c r="I30" s="25"/>
+    </row>
+    <row r="31" spans="2:9" s="4" customFormat="1">
       <c r="B31" s="26" t="s">
         <v>11</v>
       </c>
@@ -2417,16 +2405,15 @@
       </c>
       <c r="E31" s="28"/>
       <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
+      <c r="G31" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H31" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I31" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J31" s="29"/>
-    </row>
-    <row r="32" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I31" s="29"/>
+    </row>
+    <row r="32" spans="2:9" s="4" customFormat="1">
       <c r="B32" s="26" t="s">
         <v>11</v>
       </c>
@@ -2436,16 +2423,15 @@
       </c>
       <c r="E32" s="28"/>
       <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="G32" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H32" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" s="29"/>
-    </row>
-    <row r="33" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I32" s="29"/>
+    </row>
+    <row r="33" spans="2:9" s="4" customFormat="1">
       <c r="B33" s="26" t="s">
         <v>11</v>
       </c>
@@ -2455,16 +2441,15 @@
       </c>
       <c r="E33" s="28"/>
       <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="G33" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H33" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I33" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J33" s="29"/>
-    </row>
-    <row r="34" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I33" s="29"/>
+    </row>
+    <row r="34" spans="2:9" s="4" customFormat="1">
       <c r="B34" s="26" t="s">
         <v>11</v>
       </c>
@@ -2474,16 +2459,15 @@
       </c>
       <c r="E34" s="28"/>
       <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="G34" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H34" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I34" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J34" s="29"/>
-    </row>
-    <row r="35" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I34" s="29"/>
+    </row>
+    <row r="35" spans="2:9" s="4" customFormat="1">
       <c r="B35" s="30" t="s">
         <v>11</v>
       </c>
@@ -2493,36 +2477,34 @@
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I35" s="31"/>
-      <c r="J35" s="33"/>
-    </row>
-    <row r="36" spans="2:10" s="4" customFormat="1">
+      <c r="G35" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="31"/>
+      <c r="I35" s="33"/>
+    </row>
+    <row r="36" spans="2:9" s="4" customFormat="1">
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="2:10" s="4" customFormat="1" ht="110.25">
+    <row r="37" spans="2:9" s="4" customFormat="1" ht="110.25">
       <c r="B37" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="24" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="25"/>
-    </row>
-    <row r="38" spans="2:10" s="4" customFormat="1">
+      <c r="I37" s="25"/>
+    </row>
+    <row r="38" spans="2:9" s="4" customFormat="1">
       <c r="B38" s="26" t="s">
         <v>11</v>
       </c>
@@ -2532,16 +2514,15 @@
       </c>
       <c r="E38" s="28"/>
       <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="G38" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H38" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I38" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J38" s="29"/>
-    </row>
-    <row r="39" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I38" s="29"/>
+    </row>
+    <row r="39" spans="2:9" s="4" customFormat="1">
       <c r="B39" s="26" t="s">
         <v>11</v>
       </c>
@@ -2551,16 +2532,15 @@
       </c>
       <c r="E39" s="28"/>
       <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="G39" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H39" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="29"/>
-    </row>
-    <row r="40" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I39" s="29"/>
+    </row>
+    <row r="40" spans="2:9" s="4" customFormat="1">
       <c r="B40" s="26" t="s">
         <v>11</v>
       </c>
@@ -2570,16 +2550,15 @@
       </c>
       <c r="E40" s="28"/>
       <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="G40" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H40" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I40" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J40" s="29"/>
-    </row>
-    <row r="41" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I40" s="29"/>
+    </row>
+    <row r="41" spans="2:9" s="4" customFormat="1">
       <c r="B41" s="26" t="s">
         <v>11</v>
       </c>
@@ -2589,16 +2568,15 @@
       </c>
       <c r="E41" s="28"/>
       <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
+      <c r="G41" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H41" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I41" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="29"/>
-    </row>
-    <row r="42" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I41" s="29"/>
+    </row>
+    <row r="42" spans="2:9" s="4" customFormat="1">
       <c r="B42" s="30" t="s">
         <v>11</v>
       </c>
@@ -2608,39 +2586,37 @@
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I42" s="31"/>
-      <c r="J42" s="33"/>
-    </row>
-    <row r="43" spans="2:10" s="4" customFormat="1">
+      <c r="G42" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H42" s="31"/>
+      <c r="I42" s="33"/>
+    </row>
+    <row r="43" spans="2:9" s="4" customFormat="1">
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="2:10" s="4" customFormat="1">
+    <row r="44" spans="2:9" s="4" customFormat="1">
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="2:10" s="4" customFormat="1" ht="141.75">
+    <row r="45" spans="2:9" s="4" customFormat="1" ht="141.75">
       <c r="B45" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D45" s="23"/>
       <c r="E45" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
-      <c r="I45" s="23"/>
-      <c r="J45" s="25"/>
-    </row>
-    <row r="46" spans="2:10" s="4" customFormat="1">
+      <c r="I45" s="25"/>
+    </row>
+    <row r="46" spans="2:9" s="4" customFormat="1">
       <c r="B46" s="26" t="s">
         <v>11</v>
       </c>
@@ -2650,16 +2626,15 @@
       </c>
       <c r="E46" s="28"/>
       <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="G46" s="27" t="s">
+        <v>46</v>
+      </c>
       <c r="H46" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I46" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="J46" s="29"/>
-    </row>
-    <row r="47" spans="2:10" s="4" customFormat="1">
+        <v>35</v>
+      </c>
+      <c r="I46" s="29"/>
+    </row>
+    <row r="47" spans="2:9" s="4" customFormat="1">
       <c r="B47" s="26" t="s">
         <v>11</v>
       </c>
@@ -2669,16 +2644,15 @@
       </c>
       <c r="E47" s="28"/>
       <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
+      <c r="G47" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="H47" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I47" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J47" s="29"/>
-    </row>
-    <row r="48" spans="2:10" s="4" customFormat="1">
+        <v>36</v>
+      </c>
+      <c r="I47" s="29"/>
+    </row>
+    <row r="48" spans="2:9" s="4" customFormat="1">
       <c r="B48" s="26" t="s">
         <v>11</v>
       </c>
@@ -2688,16 +2662,15 @@
       </c>
       <c r="E48" s="28"/>
       <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="G48" s="27" t="s">
+        <v>44</v>
+      </c>
       <c r="H48" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="I48" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J48" s="29"/>
-    </row>
-    <row r="49" spans="2:10" s="4" customFormat="1">
+        <v>37</v>
+      </c>
+      <c r="I48" s="29"/>
+    </row>
+    <row r="49" spans="2:9" s="4" customFormat="1">
       <c r="B49" s="26" t="s">
         <v>11</v>
       </c>
@@ -2707,16 +2680,15 @@
       </c>
       <c r="E49" s="28"/>
       <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
+      <c r="G49" s="27" t="s">
+        <v>45</v>
+      </c>
       <c r="H49" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I49" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="29"/>
-    </row>
-    <row r="50" spans="2:10" s="4" customFormat="1">
+        <v>38</v>
+      </c>
+      <c r="I49" s="29"/>
+    </row>
+    <row r="50" spans="2:9" s="4" customFormat="1">
       <c r="B50" s="30" t="s">
         <v>11</v>
       </c>
@@ -2726,139 +2698,127 @@
       </c>
       <c r="E50" s="32"/>
       <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I50" s="31"/>
-      <c r="J50" s="33"/>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="G50" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H50" s="31"/>
+      <c r="I50" s="33"/>
+    </row>
+    <row r="52" spans="2:9">
       <c r="B52" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D52" s="23"/>
       <c r="E52" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F52" s="23"/>
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="25"/>
-    </row>
-    <row r="53" spans="2:10">
+      <c r="I52" s="25"/>
+    </row>
+    <row r="53" spans="2:9" ht="31.5">
       <c r="B53" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="27"/>
       <c r="D53" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E53" s="28"/>
-      <c r="F53" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H53" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="27"/>
-      <c r="J53" s="29"/>
-    </row>
-    <row r="54" spans="2:10">
+      <c r="F53" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G53" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H53" s="27"/>
+      <c r="I53" s="29"/>
+    </row>
+    <row r="54" spans="2:9">
       <c r="B54" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="31"/>
       <c r="D54" s="31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E54" s="32"/>
       <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I54" s="31"/>
-      <c r="J54" s="33"/>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="G54" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H54" s="31"/>
+      <c r="I54" s="33"/>
+    </row>
+    <row r="56" spans="2:9">
       <c r="B56" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
       <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="25"/>
-    </row>
-    <row r="57" spans="2:10">
+      <c r="I56" s="25"/>
+    </row>
+    <row r="57" spans="2:9">
       <c r="B57" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="31"/>
       <c r="D57" s="31" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E57" s="32"/>
       <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" s="31"/>
-      <c r="J57" s="33"/>
-    </row>
-    <row r="60" spans="2:10" ht="31.5">
+      <c r="G57" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H57" s="31"/>
+      <c r="I57" s="33"/>
+    </row>
+    <row r="60" spans="2:9" ht="31.5">
       <c r="B60" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D60" s="23"/>
       <c r="E60" s="24" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
       <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="25"/>
-    </row>
-    <row r="61" spans="2:10">
+      <c r="I60" s="25"/>
+    </row>
+    <row r="61" spans="2:9" ht="31.5">
       <c r="B61" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="31"/>
       <c r="D61" s="31" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E61" s="32"/>
-      <c r="F61" s="31" t="s">
-        <v>67</v>
+      <c r="F61" s="32" t="s">
+        <v>78</v>
       </c>
       <c r="G61" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="H61" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I61" s="31"/>
-      <c r="J61" s="33"/>
+        <v>41</v>
+      </c>
+      <c r="H61" s="31"/>
+      <c r="I61" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/dialog_v2.xlsx
+++ b/xls/dialog_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="karen" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="86">
   <si>
     <t>section</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -174,13 +174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>!_first_meet:
-很高興認識你，我是Karen
-true:
-你好;需要幫助嗎?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>post</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,10 +267,6 @@
   </si>
   <si>
     <t>完成了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>n_quest_01_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -357,15 +346,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>qk01==going : 任務如何了?;
-qk01==done : 很好，這是你的獎勵</t>
+    <t>qk01==going : 任務如何了? ;
+qk01==done : 任務如何了? ;
+qk01==close : 很好，這是你的獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n_quest_01_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_quest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm _quest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>!_first_meet :
 很高興認識你，我是Karen;
 true :
-你好;需要幫助嗎?</t>
+你好/需要幫助嗎?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!_first_meet:
+很高興認識你，我是Xi;
+true:
+你好/需要幫助嗎?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1002,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>10</v>
@@ -1026,7 +1035,7 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -1037,12 +1046,12 @@
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1058,7 +1067,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -1089,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>10</v>
@@ -1106,11 +1115,11 @@
         <v>13</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -1146,7 +1155,7 @@
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="17">
@@ -1159,14 +1168,16 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="I11" s="17">
         <v>30</v>
       </c>
@@ -1191,13 +1202,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="B13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
       <c r="E13" s="20"/>
       <c r="F13" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
@@ -1208,7 +1219,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="24" t="s">
@@ -1230,7 +1241,7 @@
       <c r="E16" s="28"/>
       <c r="F16" s="27"/>
       <c r="G16" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H16" s="27" t="s">
         <v>35</v>
@@ -1248,7 +1259,7 @@
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
       <c r="G17" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="27" t="s">
         <v>36</v>
@@ -1266,7 +1277,7 @@
       <c r="E18" s="28"/>
       <c r="F18" s="27"/>
       <c r="G18" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H18" s="27" t="s">
         <v>37</v>
@@ -1284,7 +1295,7 @@
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
       <c r="G19" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" s="27" t="s">
         <v>38</v>
@@ -1302,7 +1313,7 @@
       <c r="E20" s="32"/>
       <c r="F20" s="31"/>
       <c r="G20" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="33"/>
@@ -1315,14 +1326,14 @@
         <v>13</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="24" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
@@ -1339,7 +1350,7 @@
       <c r="E23" s="28"/>
       <c r="F23" s="27"/>
       <c r="G23" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H23" s="27" t="s">
         <v>35</v>
@@ -1357,7 +1368,7 @@
       <c r="E24" s="28"/>
       <c r="F24" s="27"/>
       <c r="G24" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H24" s="27" t="s">
         <v>36</v>
@@ -1375,7 +1386,7 @@
       <c r="E25" s="28"/>
       <c r="F25" s="27"/>
       <c r="G25" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H25" s="27" t="s">
         <v>37</v>
@@ -1393,7 +1404,7 @@
       <c r="E26" s="28"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H26" s="27" t="s">
         <v>38</v>
@@ -1411,7 +1422,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="31"/>
       <c r="G27" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="33"/>
@@ -1424,14 +1435,14 @@
         <v>13</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="24" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
@@ -1448,7 +1459,7 @@
       <c r="E30" s="28"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H30" s="27" t="s">
         <v>35</v>
@@ -1466,7 +1477,7 @@
       <c r="E31" s="28"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H31" s="27" t="s">
         <v>36</v>
@@ -1484,7 +1495,7 @@
       <c r="E32" s="28"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H32" s="27" t="s">
         <v>37</v>
@@ -1502,7 +1513,7 @@
       <c r="E33" s="28"/>
       <c r="F33" s="27"/>
       <c r="G33" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H33" s="27" t="s">
         <v>38</v>
@@ -1520,7 +1531,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="31"/>
       <c r="G34" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H34" s="31"/>
       <c r="I34" s="33"/>
@@ -1533,14 +1544,14 @@
         <v>13</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="24" t="s">
         <v>26</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
@@ -1557,7 +1568,7 @@
       <c r="E37" s="28"/>
       <c r="F37" s="27"/>
       <c r="G37" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H37" s="27" t="s">
         <v>35</v>
@@ -1575,7 +1586,7 @@
       <c r="E38" s="28"/>
       <c r="F38" s="27"/>
       <c r="G38" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H38" s="27" t="s">
         <v>36</v>
@@ -1593,7 +1604,7 @@
       <c r="E39" s="28"/>
       <c r="F39" s="27"/>
       <c r="G39" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H39" s="27" t="s">
         <v>37</v>
@@ -1611,7 +1622,7 @@
       <c r="E40" s="28"/>
       <c r="F40" s="27"/>
       <c r="G40" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H40" s="27" t="s">
         <v>38</v>
@@ -1629,7 +1640,7 @@
       <c r="E41" s="32"/>
       <c r="F41" s="31"/>
       <c r="G41" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="33"/>
@@ -1645,14 +1656,14 @@
         <v>13</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
@@ -1669,7 +1680,7 @@
       <c r="E45" s="28"/>
       <c r="F45" s="27"/>
       <c r="G45" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H45" s="27" t="s">
         <v>35</v>
@@ -1687,7 +1698,7 @@
       <c r="E46" s="28"/>
       <c r="F46" s="27"/>
       <c r="G46" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H46" s="27" t="s">
         <v>36</v>
@@ -1705,7 +1716,7 @@
       <c r="E47" s="28"/>
       <c r="F47" s="27"/>
       <c r="G47" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H47" s="27" t="s">
         <v>37</v>
@@ -1723,7 +1734,7 @@
       <c r="E48" s="28"/>
       <c r="F48" s="27"/>
       <c r="G48" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H48" s="27" t="s">
         <v>38</v>
@@ -1741,7 +1752,7 @@
       <c r="E49" s="32"/>
       <c r="F49" s="31"/>
       <c r="G49" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="33"/>
@@ -1751,7 +1762,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="24" t="s">
@@ -1772,10 +1783,10 @@
       </c>
       <c r="E52" s="28"/>
       <c r="F52" s="28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H52" s="27"/>
       <c r="I52" s="29"/>
@@ -1791,7 +1802,7 @@
       <c r="E53" s="32"/>
       <c r="F53" s="31"/>
       <c r="G53" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H53" s="31"/>
       <c r="I53" s="33"/>
@@ -1801,11 +1812,11 @@
         <v>13</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D55" s="23"/>
       <c r="E55" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
@@ -1818,26 +1829,26 @@
       </c>
       <c r="C56" s="31"/>
       <c r="D56" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="31"/>
       <c r="G56" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H56" s="31"/>
       <c r="I56" s="33"/>
     </row>
-    <row r="58" spans="2:9" ht="31.5">
+    <row r="58" spans="2:9" ht="47.25">
       <c r="B58" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
@@ -1850,15 +1861,15 @@
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E59" s="28"/>
       <c r="F59" s="27"/>
       <c r="G59" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I59" s="29"/>
     </row>
@@ -1868,17 +1879,17 @@
       </c>
       <c r="C60" s="31"/>
       <c r="D60" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E60" s="32"/>
       <c r="F60" s="31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G60" s="31" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I60" s="33"/>
     </row>
@@ -1891,12 +1902,14 @@
         <v>17</v>
       </c>
       <c r="E61" s="32"/>
-      <c r="F61" s="31"/>
+      <c r="F61" s="31" t="s">
+        <v>83</v>
+      </c>
       <c r="G61" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I61" s="33"/>
     </row>
@@ -1940,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>10</v>
@@ -1975,12 +1988,12 @@
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1996,7 +2009,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -2027,7 +2040,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>10</v>
@@ -2044,11 +2057,11 @@
         <v>13</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -2084,7 +2097,7 @@
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="17">
@@ -2097,12 +2110,12 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="17">
@@ -2115,15 +2128,15 @@
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I12" s="17">
         <v>40</v>
@@ -2149,13 +2162,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
@@ -2166,7 +2179,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="24" t="s">
@@ -2188,7 +2201,7 @@
       <c r="E17" s="28"/>
       <c r="F17" s="27"/>
       <c r="G17" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" s="27" t="s">
         <v>35</v>
@@ -2206,7 +2219,7 @@
       <c r="E18" s="28"/>
       <c r="F18" s="27"/>
       <c r="G18" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H18" s="27" t="s">
         <v>36</v>
@@ -2224,7 +2237,7 @@
       <c r="E19" s="28"/>
       <c r="F19" s="27"/>
       <c r="G19" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H19" s="27" t="s">
         <v>37</v>
@@ -2242,7 +2255,7 @@
       <c r="E20" s="28"/>
       <c r="F20" s="27"/>
       <c r="G20" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H20" s="27" t="s">
         <v>38</v>
@@ -2260,7 +2273,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="31"/>
       <c r="G21" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="33"/>
@@ -2273,14 +2286,14 @@
         <v>13</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="24" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -2297,7 +2310,7 @@
       <c r="E24" s="28"/>
       <c r="F24" s="27"/>
       <c r="G24" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H24" s="27" t="s">
         <v>35</v>
@@ -2315,7 +2328,7 @@
       <c r="E25" s="28"/>
       <c r="F25" s="27"/>
       <c r="G25" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H25" s="27" t="s">
         <v>36</v>
@@ -2333,7 +2346,7 @@
       <c r="E26" s="28"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="27" t="s">
         <v>37</v>
@@ -2351,7 +2364,7 @@
       <c r="E27" s="28"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H27" s="27" t="s">
         <v>38</v>
@@ -2369,7 +2382,7 @@
       <c r="E28" s="32"/>
       <c r="F28" s="31"/>
       <c r="G28" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="31"/>
       <c r="I28" s="33"/>
@@ -2382,14 +2395,14 @@
         <v>13</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="24" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
@@ -2406,7 +2419,7 @@
       <c r="E31" s="28"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H31" s="27" t="s">
         <v>35</v>
@@ -2424,7 +2437,7 @@
       <c r="E32" s="28"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H32" s="27" t="s">
         <v>36</v>
@@ -2442,7 +2455,7 @@
       <c r="E33" s="28"/>
       <c r="F33" s="27"/>
       <c r="G33" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H33" s="27" t="s">
         <v>37</v>
@@ -2460,7 +2473,7 @@
       <c r="E34" s="28"/>
       <c r="F34" s="27"/>
       <c r="G34" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H34" s="27" t="s">
         <v>38</v>
@@ -2478,7 +2491,7 @@
       <c r="E35" s="32"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H35" s="31"/>
       <c r="I35" s="33"/>
@@ -2491,14 +2504,14 @@
         <v>13</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="24" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
@@ -2515,7 +2528,7 @@
       <c r="E38" s="28"/>
       <c r="F38" s="27"/>
       <c r="G38" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H38" s="27" t="s">
         <v>35</v>
@@ -2533,7 +2546,7 @@
       <c r="E39" s="28"/>
       <c r="F39" s="27"/>
       <c r="G39" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H39" s="27" t="s">
         <v>36</v>
@@ -2551,7 +2564,7 @@
       <c r="E40" s="28"/>
       <c r="F40" s="27"/>
       <c r="G40" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H40" s="27" t="s">
         <v>37</v>
@@ -2569,7 +2582,7 @@
       <c r="E41" s="28"/>
       <c r="F41" s="27"/>
       <c r="G41" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H41" s="27" t="s">
         <v>38</v>
@@ -2587,7 +2600,7 @@
       <c r="E42" s="32"/>
       <c r="F42" s="31"/>
       <c r="G42" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H42" s="31"/>
       <c r="I42" s="33"/>
@@ -2603,14 +2616,14 @@
         <v>13</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="23"/>
       <c r="E45" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
@@ -2627,7 +2640,7 @@
       <c r="E46" s="28"/>
       <c r="F46" s="27"/>
       <c r="G46" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H46" s="27" t="s">
         <v>35</v>
@@ -2645,7 +2658,7 @@
       <c r="E47" s="28"/>
       <c r="F47" s="27"/>
       <c r="G47" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H47" s="27" t="s">
         <v>36</v>
@@ -2663,7 +2676,7 @@
       <c r="E48" s="28"/>
       <c r="F48" s="27"/>
       <c r="G48" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H48" s="27" t="s">
         <v>37</v>
@@ -2681,7 +2694,7 @@
       <c r="E49" s="28"/>
       <c r="F49" s="27"/>
       <c r="G49" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H49" s="27" t="s">
         <v>38</v>
@@ -2699,7 +2712,7 @@
       <c r="E50" s="32"/>
       <c r="F50" s="31"/>
       <c r="G50" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="33"/>
@@ -2709,7 +2722,7 @@
         <v>13</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D52" s="23"/>
       <c r="E52" s="24" t="s">
@@ -2730,10 +2743,10 @@
       </c>
       <c r="E53" s="28"/>
       <c r="F53" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G53" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H53" s="27"/>
       <c r="I53" s="29"/>
@@ -2749,7 +2762,7 @@
       <c r="E54" s="32"/>
       <c r="F54" s="31"/>
       <c r="G54" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H54" s="31"/>
       <c r="I54" s="33"/>
@@ -2759,11 +2772,11 @@
         <v>13</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
@@ -2776,12 +2789,12 @@
       </c>
       <c r="C57" s="31"/>
       <c r="D57" s="31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E57" s="32"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H57" s="31"/>
       <c r="I57" s="33"/>
@@ -2791,11 +2804,11 @@
         <v>13</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D60" s="23"/>
       <c r="E60" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
@@ -2808,14 +2821,14 @@
       </c>
       <c r="C61" s="31"/>
       <c r="D61" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E61" s="32"/>
       <c r="F61" s="32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G61" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H61" s="31"/>
       <c r="I61" s="33"/>

--- a/xls/dialog_v2.xlsx
+++ b/xls/dialog_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="karen" sheetId="1" r:id="rId1"/>
@@ -218,10 +218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#_quest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>n_quest_01_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -309,21 +305,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>qk01==going</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qk01==done</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qk01==close</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>set qk01_report</t>
-  </si>
-  <si>
     <t>rm qk01_start ;
 set qk01_talk_xi</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -341,17 +322,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>quest q_karen_01 ;
-set _quest n_quest_01_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qk01==going : 任務如何了? ;
-qk01==done : 任務如何了? ;
-qk01==close : 很好，這是你的獎勵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>n_quest_01_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -375,6 +345,37 @@
 很高興認識你，我是Xi;
 true:
 你好/需要幫助嗎?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[_quest]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#QK01==open</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#QK01==done</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#QK01==close</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#QK01==open : 任務如何了? ;
+#QK01==done : 任務如何了? ;
+#QK01==close : 很好，這是你的獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qstart QK01 ;
+set _quest n_quest_01_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qclose QK01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1011,7 +1012,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>10</v>
@@ -1051,7 +1052,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1067,7 +1068,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -1098,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>10</v>
@@ -1119,7 +1120,7 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -1173,10 +1174,10 @@
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I11" s="17">
         <v>30</v>
@@ -1208,7 +1209,7 @@
       <c r="D13" s="19"/>
       <c r="E13" s="20"/>
       <c r="F13" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
@@ -1333,7 +1334,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
@@ -1442,7 +1443,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
@@ -1551,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
@@ -1663,7 +1664,7 @@
         <v>27</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
@@ -1783,10 +1784,10 @@
       </c>
       <c r="E52" s="28"/>
       <c r="F52" s="28" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H52" s="27"/>
       <c r="I52" s="29"/>
@@ -1812,11 +1813,11 @@
         <v>13</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" s="23"/>
       <c r="E55" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
@@ -1829,7 +1830,7 @@
       </c>
       <c r="C56" s="31"/>
       <c r="D56" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="31"/>
@@ -1844,11 +1845,11 @@
         <v>13</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
@@ -1861,7 +1862,7 @@
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E59" s="28"/>
       <c r="F59" s="27"/>
@@ -1869,7 +1870,7 @@
         <v>40</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I59" s="29"/>
     </row>
@@ -1879,17 +1880,17 @@
       </c>
       <c r="C60" s="31"/>
       <c r="D60" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E60" s="32"/>
       <c r="F60" s="31" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G60" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H60" s="31" t="s">
         <v>81</v>
-      </c>
-      <c r="H60" s="31" t="s">
-        <v>73</v>
       </c>
       <c r="I60" s="33"/>
     </row>
@@ -1903,13 +1904,13 @@
       </c>
       <c r="E61" s="32"/>
       <c r="F61" s="31" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G61" s="31" t="s">
         <v>40</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I61" s="33"/>
     </row>
@@ -1953,7 +1954,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>10</v>
@@ -1993,7 +1994,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -2009,7 +2010,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -2040,7 +2041,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>10</v>
@@ -2061,7 +2062,7 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -2115,7 +2116,7 @@
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="17">
@@ -2128,15 +2129,15 @@
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" s="17">
         <v>40</v>
@@ -2168,7 +2169,7 @@
       <c r="D14" s="19"/>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
@@ -2293,7 +2294,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -2402,7 +2403,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
@@ -2511,7 +2512,7 @@
         <v>26</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
@@ -2623,7 +2624,7 @@
         <v>27</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
@@ -2743,7 +2744,7 @@
       </c>
       <c r="E53" s="28"/>
       <c r="F53" s="28" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G53" s="31" t="s">
         <v>40</v>
@@ -2772,11 +2773,11 @@
         <v>13</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F56" s="23"/>
       <c r="G56" s="23"/>
@@ -2789,7 +2790,7 @@
       </c>
       <c r="C57" s="31"/>
       <c r="D57" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E57" s="32"/>
       <c r="F57" s="31"/>
@@ -2804,11 +2805,11 @@
         <v>13</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" s="23"/>
       <c r="E60" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F60" s="23"/>
       <c r="G60" s="23"/>
@@ -2821,11 +2822,11 @@
       </c>
       <c r="C61" s="31"/>
       <c r="D61" s="31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E61" s="32"/>
       <c r="F61" s="32" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G61" s="31" t="s">
         <v>40</v>

--- a/xls/dialog_v2.xlsx
+++ b/xls/dialog_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="karen" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="83">
   <si>
     <t>section</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -210,34 +210,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>n_quest_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>關於任務</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>n_quest_01_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任務如何了?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>關於黑森林討伐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>n_qk01_start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>前往黑森林，擊殺黑森林的野狼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -254,10 +234,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>n_quest_01_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>處理中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -271,10 +247,6 @@
   </si>
   <si>
     <t>actions</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>!_first_meet : set _quest n_quest_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -310,11 +282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>quest q_karen_01 ;
-set _quest n_quest_01_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>clr _where ;
 clr _weapon ;
 clr _eat ;
@@ -322,10 +289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>n_quest_01_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>_quest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -370,12 +333,36 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>qclose QK01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!_first_meet : set _quest n_QK01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n_QK01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n_QK01-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n_QK01-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>qstart QK01 ;
-set _quest n_quest_01_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qclose QK01</t>
+set _quest n_QK01-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_quest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n_QK01_start</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1012,7 +999,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>10</v>
@@ -1052,7 +1039,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1068,7 +1055,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="11" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -1099,7 +1086,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>10</v>
@@ -1120,7 +1107,7 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -1169,15 +1156,15 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17">
         <v>30</v>
@@ -1209,7 +1196,7 @@
       <c r="D13" s="19"/>
       <c r="E13" s="20"/>
       <c r="F13" s="19" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
@@ -1334,7 +1321,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
@@ -1443,7 +1430,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
@@ -1552,7 +1539,7 @@
         <v>26</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
@@ -1664,7 +1651,7 @@
         <v>27</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
@@ -1763,7 +1750,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="24" t="s">
@@ -1784,10 +1771,10 @@
       </c>
       <c r="E52" s="28"/>
       <c r="F52" s="28" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="H52" s="27"/>
       <c r="I52" s="29"/>
@@ -1813,11 +1800,11 @@
         <v>13</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D55" s="23"/>
       <c r="E55" s="24" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F55" s="23"/>
       <c r="G55" s="23"/>
@@ -1830,7 +1817,7 @@
       </c>
       <c r="C56" s="31"/>
       <c r="D56" s="31" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="31"/>
@@ -1845,11 +1832,11 @@
         <v>13</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="24" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
@@ -1862,7 +1849,7 @@
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="27" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E59" s="28"/>
       <c r="F59" s="27"/>
@@ -1870,7 +1857,7 @@
         <v>40</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I59" s="29"/>
     </row>
@@ -1880,17 +1867,17 @@
       </c>
       <c r="C60" s="31"/>
       <c r="D60" s="31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E60" s="32"/>
       <c r="F60" s="31" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G60" s="31" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I60" s="33"/>
     </row>
@@ -1904,13 +1891,13 @@
       </c>
       <c r="E61" s="32"/>
       <c r="F61" s="31" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G61" s="31" t="s">
         <v>40</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I61" s="33"/>
     </row>
@@ -1923,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="3.875" style="2" customWidth="1"/>
@@ -1954,7 +1941,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>10</v>
@@ -1994,7 +1981,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -2009,9 +1996,7 @@
       <c r="C4" s="11"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
-      <c r="F4" s="11" t="s">
-        <v>64</v>
-      </c>
+      <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="13"/>
@@ -2041,7 +2026,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>10</v>
@@ -2062,7 +2047,7 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -2111,14 +2096,16 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="15"/>
+        <v>70</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="I11" s="17">
         <v>30</v>
       </c>
@@ -2129,15 +2116,15 @@
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I12" s="17">
         <v>40</v>
@@ -2169,7 +2156,7 @@
       <c r="D14" s="19"/>
       <c r="E14" s="20"/>
       <c r="F14" s="19" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
@@ -2294,7 +2281,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -2403,7 +2390,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
@@ -2512,7 +2499,7 @@
         <v>26</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
@@ -2624,7 +2611,7 @@
         <v>27</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
@@ -2718,121 +2705,39 @@
       <c r="H50" s="31"/>
       <c r="I50" s="33"/>
     </row>
-    <row r="52" spans="2:9">
-      <c r="B52" s="22" t="s">
+    <row r="53" spans="2:9" ht="31.5">
+      <c r="B53" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="25"/>
-    </row>
-    <row r="53" spans="2:9" ht="31.5">
-      <c r="B53" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="G53" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H53" s="27"/>
-      <c r="I53" s="29"/>
-    </row>
-    <row r="54" spans="2:9">
+      <c r="C53" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="23"/>
+      <c r="E53" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="25"/>
+    </row>
+    <row r="54" spans="2:9" ht="31.5">
       <c r="B54" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="31"/>
       <c r="D54" s="31" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E54" s="32"/>
-      <c r="F54" s="31"/>
+      <c r="F54" s="32" t="s">
+        <v>64</v>
+      </c>
       <c r="G54" s="31" t="s">
         <v>40</v>
       </c>
       <c r="H54" s="31"/>
       <c r="I54" s="33"/>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D56" s="23"/>
-      <c r="E56" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="25"/>
-    </row>
-    <row r="57" spans="2:9">
-      <c r="B57" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H57" s="31"/>
-      <c r="I57" s="33"/>
-    </row>
-    <row r="60" spans="2:9" ht="31.5">
-      <c r="B60" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D60" s="23"/>
-      <c r="E60" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="25"/>
-    </row>
-    <row r="61" spans="2:9" ht="31.5">
-      <c r="B61" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="G61" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H61" s="31"/>
-      <c r="I61" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
